--- a/analysis/baseline_2025_26.xlsx
+++ b/analysis/baseline_2025_26.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E744"/>
+  <dimension ref="A1:E742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4402,12 +4402,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Antoine Semenyo</t>
+          <t>Virgil van Dijk</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Cody Gakpo</t>
+          <t>Antoine Semenyo</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Dominik Szoboszlai</t>
+          <t>Ismaïla Sarr</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
+          <t>Richarlison de Andrade</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Ismaïla Sarr</t>
+          <t>Dominik Szoboszlai</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -4602,12 +4602,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Virgil van Dijk</t>
+          <t>Cody Gakpo</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Richarlison de Andrade</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4657,7 +4657,7 @@
       <c r="D198" s="5" t="inlineStr"/>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>64  [Bench Boost week: bench 15 not in path; chip read]</t>
+          <t>67  [Bench Boost week: bench 12 not in path; chip read]</t>
         </is>
       </c>
     </row>
@@ -10528,12 +10528,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Erling Haaland</t>
+          <t>Rayan Cherki</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Tammy Abraham</t>
+          <t>Erling Haaland</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -10603,12 +10603,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Phil Foden</t>
+          <t>Omar Alderete</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Omar Alderete</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
+          <t>Richarlison de Andrade</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10691,7 +10691,7 @@
       <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Tammy Abraham in for Richarlison de Andrade</t>
+          <t>Rayan Cherki in for Phil Foden</t>
         </is>
       </c>
       <c r="C470" t="inlineStr"/>
@@ -10904,7 +10904,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Ismaïla Sarr</t>
+          <t>Matheus Santos Carneiro da Cunha</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Matheus Santos Carneiro da Cunha</t>
+          <t>Rayan Cherki</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Tammy Abraham</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -11054,7 +11054,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
+          <t>Richarlison de Andrade</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -11084,7 +11084,7 @@
       <c r="D487" s="5" t="inlineStr"/>
       <c r="E487" s="5" t="inlineStr">
         <is>
-          <t>77 (73 after hits)</t>
+          <t>76</t>
         </is>
       </c>
     </row>
@@ -11101,25 +11101,39 @@
     </row>
     <row r="489">
       <c r="A489" t="inlineStr"/>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>Ismaïla Sarr in for Phil Foden (-4 hit)</t>
+      <c r="B489" s="1" t="inlineStr">
+        <is>
+          <t>CHIP: Triple Captain</t>
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
     </row>
-    <row r="490">
-      <c r="A490" t="inlineStr"/>
-      <c r="B490" s="1" t="inlineStr">
-        <is>
-          <t>CHIP: Triple Captain</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr"/>
-      <c r="E490" t="inlineStr"/>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>27</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Robin Roefs</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -11127,12 +11141,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Robin Roefs</t>
+          <t>Gabriel dos Santos Magalhães</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -11142,7 +11156,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11166,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Gabriel dos Santos Magalhães</t>
+          <t>Jurriën Timber</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -11167,7 +11181,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -11177,7 +11191,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Jurriën Timber</t>
+          <t>Omar Alderete</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -11192,7 +11206,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11216,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Omar Alderete</t>
+          <t>Tyrick Mitchell</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -11217,7 +11231,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -11227,12 +11241,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Tyrick Mitchell</t>
+          <t>Antoine Semenyo</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -11242,7 +11256,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11266,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Antoine Semenyo</t>
+          <t>Declan Rice</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -11272,27 +11286,27 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="n">
+      <c r="A498" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>Cody Gakpo</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E498" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>Enzo Fernández</t>
+        </is>
+      </c>
+      <c r="C498" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D498" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E498" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11316,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Declan Rice</t>
+          <t>Rayan Cherki</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -11317,32 +11331,32 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="3" t="n">
+      <c r="A500" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B500" s="3" t="inlineStr">
-        <is>
-          <t>Enzo Fernández</t>
-        </is>
-      </c>
-      <c r="C500" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D500" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E500" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="B500" s="4" t="inlineStr">
+        <is>
+          <t>Erling Haaland</t>
+        </is>
+      </c>
+      <c r="C500" s="4" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D500" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E500" s="4" t="inlineStr">
+        <is>
+          <t>6 (12)</t>
         </is>
       </c>
     </row>
@@ -11352,12 +11366,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Ismaïla Sarr</t>
+          <t>Igor Thiago Nascimento Rodrigues</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -11372,27 +11386,27 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="4" t="n">
+      <c r="A502" t="n">
         <v>27</v>
       </c>
-      <c r="B502" s="4" t="inlineStr">
-        <is>
-          <t>Erling Haaland</t>
-        </is>
-      </c>
-      <c r="C502" s="4" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D502" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E502" s="4" t="inlineStr">
-        <is>
-          <t>6 (12)</t>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Bart Verbruggen</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Bench</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -11402,12 +11416,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Bart Verbruggen</t>
+          <t>Matheus Santos Carneiro da Cunha</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -11417,7 +11431,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11466,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Tammy Abraham</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -11467,108 +11481,108 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="n">
-        <v>27</v>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E506" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="A506" s="5" t="inlineStr">
+        <is>
+          <t>GW27 TOTAL</t>
+        </is>
+      </c>
+      <c r="B506" s="5" t="inlineStr"/>
+      <c r="C506" s="5" t="inlineStr"/>
+      <c r="D506" s="5" t="inlineStr"/>
+      <c r="E506" s="5" t="inlineStr">
+        <is>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="5" t="inlineStr">
-        <is>
-          <t>GW27 TOTAL</t>
-        </is>
-      </c>
-      <c r="B507" s="5" t="inlineStr"/>
-      <c r="C507" s="5" t="inlineStr"/>
-      <c r="D507" s="5" t="inlineStr"/>
-      <c r="E507" s="5" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr"/>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>Cody Gakpo in for Matheus Santos Carneiro da Cunha</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr"/>
-      <c r="D508" t="inlineStr"/>
-      <c r="E508" t="inlineStr"/>
+      <c r="A507" t="inlineStr"/>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Igor Thiago Nascimento Rodrigues in for Richarlison de Andrade</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr"/>
+      <c r="D507" t="inlineStr"/>
+      <c r="E507" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>28</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Bart Verbruggen</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="510">
-      <c r="A510" t="n">
+      <c r="A510" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>Bart Verbruggen</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E510" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="B510" s="3" t="inlineStr">
+        <is>
+          <t>Gabriel dos Santos Magalhães</t>
+        </is>
+      </c>
+      <c r="C510" s="3" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D510" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E510" s="3" t="inlineStr">
+        <is>
+          <t>9 (18)</t>
         </is>
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="3" t="n">
+      <c r="A511" t="n">
         <v>28</v>
       </c>
-      <c r="B511" s="3" t="inlineStr">
-        <is>
-          <t>Gabriel dos Santos Magalhães</t>
-        </is>
-      </c>
-      <c r="C511" s="3" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D511" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E511" s="3" t="inlineStr">
-        <is>
-          <t>9 (18)</t>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Jurriën Timber</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -11578,7 +11592,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Jurriën Timber</t>
+          <t>Malick Thiaw</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -11593,7 +11607,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11617,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Malick Thiaw</t>
+          <t>Omar Alderete</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -11618,7 +11632,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -11628,12 +11642,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Marc Guéhi</t>
+          <t>Antoine Semenyo</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -11643,7 +11657,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -11653,7 +11667,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Antoine Semenyo</t>
+          <t>Dango Ouattara</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -11668,7 +11682,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -11678,7 +11692,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Cody Gakpo</t>
+          <t>Declan Rice</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -11693,7 +11707,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11717,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Declan Rice</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -11718,7 +11732,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11728,7 +11742,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Enzo Fernández</t>
+          <t>Matheus Santos Carneiro da Cunha</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -11743,7 +11757,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -11753,12 +11767,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Ismaïla Sarr</t>
+          <t>Igor Thiago Nascimento Rodrigues</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -11768,7 +11782,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -11778,22 +11792,22 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Tammy Abraham</t>
+          <t>Robin Roefs</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11817,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Robin Roefs</t>
+          <t>Tyrick Mitchell</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -11818,7 +11832,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11828,12 +11842,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Omar Alderete</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -11843,85 +11857,85 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="n">
+      <c r="A523" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
-        </is>
-      </c>
-      <c r="C523" t="inlineStr">
+      <c r="B523" s="4" t="inlineStr">
+        <is>
+          <t>Erling Haaland</t>
+        </is>
+      </c>
+      <c r="C523" s="4" t="inlineStr">
         <is>
           <t>FWD</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr">
+      <c r="D523" s="4" t="inlineStr">
         <is>
           <t>Bench</t>
         </is>
       </c>
-      <c r="E523" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="E523" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B524" s="4" t="inlineStr">
-        <is>
-          <t>Erling Haaland</t>
-        </is>
-      </c>
-      <c r="C524" s="4" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D524" s="4" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E524" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="A524" s="5" t="inlineStr">
+        <is>
+          <t>GW28 TOTAL</t>
+        </is>
+      </c>
+      <c r="B524" s="5" t="inlineStr"/>
+      <c r="C524" s="5" t="inlineStr"/>
+      <c r="D524" s="5" t="inlineStr"/>
+      <c r="E524" s="5" t="inlineStr">
+        <is>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="5" t="inlineStr">
-        <is>
-          <t>GW28 TOTAL</t>
-        </is>
-      </c>
-      <c r="B525" s="5" t="inlineStr"/>
-      <c r="C525" s="5" t="inlineStr"/>
-      <c r="D525" s="5" t="inlineStr"/>
-      <c r="E525" s="5" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr"/>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>Marc Guéhi in for Tyrick Mitchell</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr"/>
-      <c r="D526" t="inlineStr"/>
-      <c r="E526" t="inlineStr"/>
+      <c r="A525" t="inlineStr"/>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Dango Ouattara in for Rayan Cherki</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr"/>
+      <c r="D525" t="inlineStr"/>
+      <c r="E525" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>29</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Bart Verbruggen</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -11929,12 +11943,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Bart Verbruggen</t>
+          <t>Gabriel dos Santos Magalhães</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -11944,7 +11958,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -11954,7 +11968,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Gabriel dos Santos Magalhães</t>
+          <t>Jurriën Timber</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -11969,7 +11983,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11993,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Jurriën Timber</t>
+          <t>Malick Thiaw</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -11994,82 +12008,82 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="531">
-      <c r="A531" t="n">
+      <c r="A531" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>Malick Thiaw</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E531" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="B531" s="4" t="inlineStr">
+        <is>
+          <t>Antoine Semenyo</t>
+        </is>
+      </c>
+      <c r="C531" s="4" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D531" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E531" s="4" t="inlineStr">
+        <is>
+          <t>7 (14)</t>
         </is>
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="n">
+      <c r="A532" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>Marc Guéhi</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E532" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="B532" s="3" t="inlineStr">
+        <is>
+          <t>Cody Gakpo</t>
+        </is>
+      </c>
+      <c r="C532" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D532" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E532" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="3" t="n">
+      <c r="A533" t="n">
         <v>29</v>
       </c>
-      <c r="B533" s="3" t="inlineStr">
-        <is>
-          <t>Antoine Semenyo</t>
-        </is>
-      </c>
-      <c r="C533" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D533" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E533" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Dango Ouattara</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12093,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Cody Gakpo</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -12094,7 +12108,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12118,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Enzo Fernández</t>
+          <t>Matheus Santos Carneiro da Cunha</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -12119,7 +12133,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12129,12 +12143,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Ismaïla Sarr</t>
+          <t>Erling Haaland</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -12144,32 +12158,32 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="4" t="n">
+      <c r="A537" t="n">
         <v>29</v>
       </c>
-      <c r="B537" s="4" t="inlineStr">
-        <is>
-          <t>Mohamed Salah</t>
-        </is>
-      </c>
-      <c r="C537" s="4" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D537" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E537" s="4" t="inlineStr">
-        <is>
-          <t>9 (18)</t>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Igor Thiago Nascimento Rodrigues</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12179,17 +12193,17 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Hugo Ekitiké</t>
+          <t>Tyrick Mitchell</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -12254,12 +12268,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Tammy Abraham</t>
+          <t>Robin Roefs</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -12269,119 +12283,133 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="5" t="inlineStr">
+        <is>
+          <t>GW29 TOTAL</t>
+        </is>
+      </c>
+      <c r="B542" s="5" t="inlineStr"/>
+      <c r="C542" s="5" t="inlineStr"/>
+      <c r="D542" s="5" t="inlineStr"/>
+      <c r="E542" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr"/>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Cody Gakpo in for Declan Rice</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr"/>
+      <c r="D543" t="inlineStr"/>
+      <c r="E543" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>30</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Bart Verbruggen</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>30</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Daniel Ballard</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B547" s="4" t="inlineStr">
+        <is>
+          <t>Gabriel dos Santos Magalhães</t>
+        </is>
+      </c>
+      <c r="C547" s="4" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D547" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E547" s="4" t="inlineStr">
+        <is>
+          <t>9 (18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>30</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Jurriën Timber</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="n">
-        <v>29</v>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>Robin Roefs</t>
-        </is>
-      </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
-      <c r="D542" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E542" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" s="5" t="inlineStr">
-        <is>
-          <t>GW29 TOTAL</t>
-        </is>
-      </c>
-      <c r="B543" s="5" t="inlineStr"/>
-      <c r="C543" s="5" t="inlineStr"/>
-      <c r="D543" s="5" t="inlineStr"/>
-      <c r="E543" s="5" t="inlineStr">
-        <is>
-          <t>80 (76 after hits)</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr"/>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>Mohamed Salah in for Declan Rice</t>
-        </is>
-      </c>
-      <c r="C544" t="inlineStr"/>
-      <c r="D544" t="inlineStr"/>
-      <c r="E544" t="inlineStr"/>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr"/>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>Hugo Ekitiké in for Erling Haaland (-4 hit)</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr"/>
-      <c r="D545" t="inlineStr"/>
-      <c r="E545" t="inlineStr"/>
-    </row>
-    <row r="547">
-      <c r="A547" t="n">
-        <v>30</v>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>Bart Verbruggen</t>
-        </is>
-      </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E547" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B548" s="3" t="inlineStr">
-        <is>
-          <t>Gabriel dos Santos Magalhães</t>
-        </is>
-      </c>
-      <c r="C548" s="3" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D548" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E548" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
     </row>
@@ -12391,12 +12419,12 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Jurriën Timber</t>
+          <t>Antoine Semenyo</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -12406,7 +12434,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12416,12 +12444,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Marc Guéhi</t>
+          <t>Cody Gakpo</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -12431,7 +12459,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -12441,12 +12469,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Omar Alderete</t>
+          <t>Dango Ouattara</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -12456,7 +12484,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -12466,7 +12494,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Antoine Semenyo</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -12491,7 +12519,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Cody Gakpo</t>
+          <t>Matheus Santos Carneiro da Cunha</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -12506,32 +12534,32 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="554">
-      <c r="A554" t="n">
+      <c r="A554" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>Dango Ouattara</t>
-        </is>
-      </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E554" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="B554" s="3" t="inlineStr">
+        <is>
+          <t>Erling Haaland</t>
+        </is>
+      </c>
+      <c r="C554" s="3" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D554" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E554" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12541,12 +12569,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Enzo Fernández</t>
+          <t>Igor Thiago Nascimento Rodrigues</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -12556,32 +12584,32 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="4" t="n">
+      <c r="A556" t="n">
         <v>30</v>
       </c>
-      <c r="B556" s="4" t="inlineStr">
-        <is>
-          <t>Mohamed Salah</t>
-        </is>
-      </c>
-      <c r="C556" s="4" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D556" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E556" s="4" t="inlineStr">
-        <is>
-          <t>1 (2)</t>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Robin Roefs</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Bench</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12591,22 +12619,22 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Hugo Ekitiké</t>
+          <t>Omar Alderete</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12616,12 +12644,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Robin Roefs</t>
+          <t>Malick Thiaw</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -12631,7 +12659,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -12641,100 +12669,100 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
+          <t>Norberto Bercique Gomes Betuncal</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Bench</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="5" t="inlineStr">
+        <is>
+          <t>GW30 TOTAL</t>
+        </is>
+      </c>
+      <c r="B560" s="5" t="inlineStr"/>
+      <c r="C560" s="5" t="inlineStr"/>
+      <c r="D560" s="5" t="inlineStr"/>
+      <c r="E560" s="5" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr"/>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Daniel Ballard in for Tyrick Mitchell</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr"/>
+      <c r="D561" t="inlineStr"/>
+      <c r="E561" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>31</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Bart Verbruggen</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B564" s="4" t="inlineStr">
+        <is>
           <t>Malick Thiaw</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D559" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="n">
-        <v>30</v>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D560" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E560" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="n">
-        <v>30</v>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>Tammy Abraham</t>
-        </is>
-      </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E561" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" s="5" t="inlineStr">
-        <is>
-          <t>GW30 TOTAL</t>
-        </is>
-      </c>
-      <c r="B562" s="5" t="inlineStr"/>
-      <c r="C562" s="5" t="inlineStr"/>
-      <c r="D562" s="5" t="inlineStr"/>
-      <c r="E562" s="5" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr"/>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>Dango Ouattara in for Ismaïla Sarr</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr"/>
-      <c r="D563" t="inlineStr"/>
-      <c r="E563" t="inlineStr"/>
+      <c r="C564" s="4" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D564" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E564" s="4" t="inlineStr">
+        <is>
+          <t>0 (0)</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -12742,12 +12770,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Bart Verbruggen</t>
+          <t>Omar Alderete</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -12757,57 +12785,57 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="4" t="n">
+      <c r="A566" t="n">
         <v>31</v>
       </c>
-      <c r="B566" s="4" t="inlineStr">
-        <is>
-          <t>Malick Thiaw</t>
-        </is>
-      </c>
-      <c r="C566" s="4" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D566" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E566" s="4" t="inlineStr">
-        <is>
-          <t>0 (0)</t>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Sepp van den Berg</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="567">
-      <c r="A567" t="n">
+      <c r="A567" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>Omar Alderete</t>
-        </is>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E567" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="B567" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Borges Fernandes</t>
+        </is>
+      </c>
+      <c r="C567" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D567" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E567" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -12817,12 +12845,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Virgil van Dijk</t>
+          <t>Cody Gakpo</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -12832,32 +12860,32 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="3" t="n">
+      <c r="A569" t="n">
         <v>31</v>
       </c>
-      <c r="B569" s="3" t="inlineStr">
-        <is>
-          <t>Bruno Borges Fernandes</t>
-        </is>
-      </c>
-      <c r="C569" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D569" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E569" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Dango Ouattara</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -12867,7 +12895,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Bryan Mbeumo</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -12892,7 +12920,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Cody Gakpo</t>
+          <t>Matheus Santos Carneiro da Cunha</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -12907,7 +12935,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -12917,12 +12945,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Dango Ouattara</t>
+          <t>Igor Thiago Nascimento Rodrigues</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -12932,7 +12960,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -12942,12 +12970,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Enzo Fernández</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -12957,7 +12985,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -12967,22 +12995,22 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Hugo Ekitiké</t>
+          <t>Robin Roefs</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12992,22 +13020,22 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
+          <t>Daniel Ballard</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -13017,12 +13045,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Robin Roefs</t>
+          <t>Erling Haaland</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -13042,12 +13070,12 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Tammy Abraham</t>
+          <t>Gabriel dos Santos Magalhães</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -13057,107 +13085,121 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="578">
-      <c r="A578" t="n">
-        <v>31</v>
-      </c>
-      <c r="B578" t="inlineStr">
+      <c r="A578" s="5" t="inlineStr">
+        <is>
+          <t>GW31 TOTAL</t>
+        </is>
+      </c>
+      <c r="B578" s="5" t="inlineStr"/>
+      <c r="C578" s="5" t="inlineStr"/>
+      <c r="D578" s="5" t="inlineStr"/>
+      <c r="E578" s="5" t="inlineStr">
+        <is>
+          <t>54 (50 after hits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr"/>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Sepp van den Berg in for Jurriën Timber</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr"/>
+      <c r="D579" t="inlineStr"/>
+      <c r="E579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr"/>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Bruno Borges Fernandes in for Antoine Semenyo (-4 hit)</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr"/>
+      <c r="D580" t="inlineStr"/>
+      <c r="E580" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>32</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Bart Verbruggen</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B583" s="4" t="inlineStr">
         <is>
           <t>Gabriel dos Santos Magalhães</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E578" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="n">
-        <v>31</v>
-      </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>Marc Guéhi</t>
-        </is>
-      </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E579" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" s="5" t="inlineStr">
-        <is>
-          <t>GW31 TOTAL</t>
-        </is>
-      </c>
-      <c r="B580" s="5" t="inlineStr"/>
-      <c r="C580" s="5" t="inlineStr"/>
-      <c r="D580" s="5" t="inlineStr"/>
-      <c r="E580" s="5" t="inlineStr">
-        <is>
-          <t>44 (36 after hits)</t>
-        </is>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" t="inlineStr"/>
-      <c r="B581" t="inlineStr">
-        <is>
-          <t>Virgil van Dijk in for Jurriën Timber</t>
-        </is>
-      </c>
-      <c r="C581" t="inlineStr"/>
-      <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr"/>
-    </row>
-    <row r="582">
-      <c r="A582" t="inlineStr"/>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>Bryan Mbeumo in for Antoine Semenyo (-4 hit)</t>
-        </is>
-      </c>
-      <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr"/>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr"/>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>Bruno Borges Fernandes in for Mohamed Salah (-4 hit)</t>
-        </is>
-      </c>
-      <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
+      <c r="C583" s="4" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D583" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E583" s="4" t="inlineStr">
+        <is>
+          <t>4 (8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>32</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Jan Paul van Hecke</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -13165,12 +13207,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Bart Verbruggen</t>
+          <t>Marc Guéhi</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -13180,32 +13222,32 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="4" t="n">
+      <c r="A586" t="n">
         <v>32</v>
       </c>
-      <c r="B586" s="4" t="inlineStr">
-        <is>
-          <t>Gabriel dos Santos Magalhães</t>
-        </is>
-      </c>
-      <c r="C586" s="4" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D586" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E586" s="4" t="inlineStr">
-        <is>
-          <t>4 (8)</t>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Nico O'Reilly</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13257,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Jan Paul van Hecke</t>
+          <t>Virgil van Dijk</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -13230,32 +13272,32 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="588">
-      <c r="A588" t="n">
+      <c r="A588" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B588" t="inlineStr">
-        <is>
-          <t>Marc Guéhi</t>
-        </is>
-      </c>
-      <c r="C588" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E588" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="B588" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Borges Fernandes</t>
+        </is>
+      </c>
+      <c r="C588" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D588" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E588" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -13265,12 +13307,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Nico O'Reilly</t>
+          <t>Cody Gakpo</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -13280,7 +13322,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -13290,12 +13332,12 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Virgil van Dijk</t>
+          <t>Diego Gómez Amarilla</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -13305,32 +13347,32 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="3" t="n">
+      <c r="A591" t="n">
         <v>32</v>
       </c>
-      <c r="B591" s="3" t="inlineStr">
-        <is>
-          <t>Bruno Borges Fernandes</t>
-        </is>
-      </c>
-      <c r="C591" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D591" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E591" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Ismaïla Sarr</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -13340,12 +13382,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Cody Gakpo</t>
+          <t>Erling Haaland</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -13355,7 +13397,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -13365,22 +13407,22 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Diego Gómez Amarilla</t>
+          <t>Karl Darlow</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -13390,22 +13432,22 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Ismaïla Sarr</t>
+          <t>João Pedro Junqueira de Jesus</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -13415,7 +13457,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Erling Haaland</t>
+          <t>Dominic Calvert-Lewin</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -13425,7 +13467,7 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -13440,12 +13482,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Karl Darlow</t>
+          <t>Marcus Tavernier</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -13455,105 +13497,63 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="597">
-      <c r="A597" t="n">
-        <v>32</v>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>João Pedro Junqueira de Jesus</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D597" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E597" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="A597" s="5" t="inlineStr">
+        <is>
+          <t>GW32 TOTAL</t>
+        </is>
+      </c>
+      <c r="B597" s="5" t="inlineStr"/>
+      <c r="C597" s="5" t="inlineStr"/>
+      <c r="D597" s="5" t="inlineStr"/>
+      <c r="E597" s="5" t="inlineStr">
+        <is>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="598">
-      <c r="A598" t="n">
-        <v>32</v>
-      </c>
+      <c r="A598" t="inlineStr"/>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Dominic Calvert-Lewin</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D598" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Marcus Tavernier in for Dango Ouattara</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr"/>
+      <c r="D598" t="inlineStr"/>
+      <c r="E598" t="inlineStr"/>
     </row>
     <row r="599">
-      <c r="A599" t="n">
-        <v>32</v>
-      </c>
+      <c r="A599" t="inlineStr"/>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Marcus Tavernier</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D599" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Jan Paul van Hecke in for Sepp van den Berg</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr"/>
+      <c r="D599" t="inlineStr"/>
+      <c r="E599" t="inlineStr"/>
     </row>
     <row r="600">
-      <c r="A600" s="5" t="inlineStr">
-        <is>
-          <t>GW32 TOTAL</t>
-        </is>
-      </c>
-      <c r="B600" s="5" t="inlineStr"/>
-      <c r="C600" s="5" t="inlineStr"/>
-      <c r="D600" s="5" t="inlineStr"/>
-      <c r="E600" s="5" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
+      <c r="A600" t="inlineStr"/>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>João Pedro Junqueira de Jesus in for Igor Thiago Nascimento Rodrigues</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr"/>
+      <c r="D600" t="inlineStr"/>
+      <c r="E600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr"/>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Marcus Tavernier in for Dango Ouattara</t>
+          <t>Diego Gómez Amarilla in for Enzo Fernández</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
@@ -13564,7 +13564,7 @@
       <c r="A602" t="inlineStr"/>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Diego Gómez Amarilla in for Bryan Mbeumo</t>
+          <t>Dominic Calvert-Lewin in for Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -13575,7 +13575,7 @@
       <c r="A603" t="inlineStr"/>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Ismaïla Sarr in for Enzo Fernández</t>
+          <t>Ismaïla Sarr in for Matheus Santos Carneiro da Cunha</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
@@ -13586,7 +13586,7 @@
       <c r="A604" t="inlineStr"/>
       <c r="B604" t="inlineStr">
         <is>
-          <t>João Pedro Junqueira de Jesus in for Norberto Bercique Gomes Betuncal</t>
+          <t>Marc Guéhi in for Daniel Ballard</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -13597,7 +13597,7 @@
       <c r="A605" t="inlineStr"/>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Erling Haaland in for Hugo Ekitiké</t>
+          <t>Karl Darlow in for Robin Roefs</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
@@ -13608,7 +13608,7 @@
       <c r="A606" t="inlineStr"/>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Karl Darlow in for Robin Roefs</t>
+          <t>Virgil van Dijk in for Omar Alderete</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -13619,7 +13619,7 @@
       <c r="A607" t="inlineStr"/>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Jan Paul van Hecke in for Omar Alderete</t>
+          <t>Nico O'Reilly in for Malick Thiaw</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -13628,57 +13628,85 @@
     </row>
     <row r="608">
       <c r="A608" t="inlineStr"/>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>Nico O'Reilly in for Malick Thiaw</t>
+      <c r="B608" s="1" t="inlineStr">
+        <is>
+          <t>CHIP: Wildcard</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr"/>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>Dominic Calvert-Lewin in for Tammy Abraham</t>
-        </is>
-      </c>
-      <c r="C609" t="inlineStr"/>
-      <c r="D609" t="inlineStr"/>
-      <c r="E609" t="inlineStr"/>
-    </row>
     <row r="610">
-      <c r="A610" t="inlineStr"/>
-      <c r="B610" s="1" t="inlineStr">
-        <is>
-          <t>CHIP: Wildcard</t>
-        </is>
-      </c>
-      <c r="C610" t="inlineStr"/>
-      <c r="D610" t="inlineStr"/>
-      <c r="E610" t="inlineStr"/>
+      <c r="A610" t="n">
+        <v>33</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Karl Darlow</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>33</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Jaka Bijol</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="612">
-      <c r="A612" t="n">
+      <c r="A612" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>Karl Darlow</t>
-        </is>
-      </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
-      <c r="D612" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E612" t="inlineStr">
+      <c r="B612" s="3" t="inlineStr">
+        <is>
+          <t>Marc Guéhi</t>
+        </is>
+      </c>
+      <c r="C612" s="3" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D612" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E612" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -13690,7 +13718,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Jaka Bijol</t>
+          <t>Nico O'Reilly</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -13705,32 +13733,32 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="3" t="n">
+      <c r="A614" t="n">
         <v>33</v>
       </c>
-      <c r="B614" s="3" t="inlineStr">
-        <is>
-          <t>Marc Guéhi</t>
-        </is>
-      </c>
-      <c r="C614" s="3" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D614" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E614" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Bruno Borges Fernandes</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -13740,12 +13768,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Nico O'Reilly</t>
+          <t>Cody Gakpo</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -13755,7 +13783,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -13765,7 +13793,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Diego Gómez Amarilla</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -13780,7 +13808,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -13790,7 +13818,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Cody Gakpo</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -13805,7 +13833,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -13815,7 +13843,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Diego Gómez Amarilla</t>
+          <t>Marcus Tavernier</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -13830,7 +13858,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -13840,12 +13868,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Enzo Fernández</t>
+          <t>Dominic Calvert-Lewin</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -13855,32 +13883,32 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="620">
-      <c r="A620" t="n">
+      <c r="A620" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>Marcus Tavernier</t>
-        </is>
-      </c>
-      <c r="C620" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D620" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E620" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="B620" s="4" t="inlineStr">
+        <is>
+          <t>Erling Haaland</t>
+        </is>
+      </c>
+      <c r="C620" s="4" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D620" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E620" s="4" t="inlineStr">
+        <is>
+          <t>13 (26)</t>
         </is>
       </c>
     </row>
@@ -13890,17 +13918,17 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Dominic Calvert-Lewin</t>
+          <t>Bart Verbruggen</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
@@ -13910,27 +13938,27 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" s="4" t="n">
+      <c r="A622" t="n">
         <v>33</v>
       </c>
-      <c r="B622" s="4" t="inlineStr">
-        <is>
-          <t>Erling Haaland</t>
-        </is>
-      </c>
-      <c r="C622" s="4" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D622" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E622" s="4" t="inlineStr">
-        <is>
-          <t>13 (26)</t>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Jan Paul van Hecke</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Bench</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -13940,12 +13968,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Bart Verbruggen</t>
+          <t>Virgil van Dijk</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -13985,102 +14013,102 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" t="n">
-        <v>33</v>
-      </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>Jan Paul van Hecke</t>
-        </is>
-      </c>
-      <c r="C625" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D625" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E625" t="inlineStr">
-        <is>
-          <t>12</t>
+      <c r="A625" s="5" t="inlineStr">
+        <is>
+          <t>GW33 TOTAL</t>
+        </is>
+      </c>
+      <c r="B625" s="5" t="inlineStr"/>
+      <c r="C625" s="5" t="inlineStr"/>
+      <c r="D625" s="5" t="inlineStr"/>
+      <c r="E625" s="5" t="inlineStr">
+        <is>
+          <t>98  [Bench Boost week: bench 28 not in path; chip read]</t>
         </is>
       </c>
     </row>
     <row r="626">
-      <c r="A626" t="n">
-        <v>33</v>
-      </c>
+      <c r="A626" t="inlineStr"/>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Virgil van Dijk</t>
-        </is>
-      </c>
-      <c r="C626" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D626" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E626" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Jaka Bijol in for Gabriel dos Santos Magalhães</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr"/>
+      <c r="D626" t="inlineStr"/>
+      <c r="E626" t="inlineStr"/>
     </row>
     <row r="627">
-      <c r="A627" s="5" t="inlineStr">
-        <is>
-          <t>GW33 TOTAL</t>
-        </is>
-      </c>
-      <c r="B627" s="5" t="inlineStr"/>
-      <c r="C627" s="5" t="inlineStr"/>
-      <c r="D627" s="5" t="inlineStr"/>
-      <c r="E627" s="5" t="inlineStr">
-        <is>
-          <t>98  [Bench Boost week: bench 28 not in path; chip read]</t>
-        </is>
-      </c>
+      <c r="A627" t="inlineStr"/>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Enzo Fernández in for Ismaïla Sarr</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr"/>
+      <c r="D627" t="inlineStr"/>
+      <c r="E627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr"/>
-      <c r="B628" t="inlineStr">
-        <is>
-          <t>Jaka Bijol in for Gabriel dos Santos Magalhães</t>
+      <c r="B628" s="1" t="inlineStr">
+        <is>
+          <t>CHIP: Bench Boost</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr"/>
       <c r="E628" t="inlineStr"/>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr"/>
-      <c r="B629" t="inlineStr">
-        <is>
-          <t>Enzo Fernández in for Ismaïla Sarr</t>
-        </is>
-      </c>
-      <c r="C629" t="inlineStr"/>
-      <c r="D629" t="inlineStr"/>
-      <c r="E629" t="inlineStr"/>
-    </row>
     <row r="630">
-      <c r="A630" t="inlineStr"/>
-      <c r="B630" s="1" t="inlineStr">
-        <is>
-          <t>CHIP: Bench Boost</t>
-        </is>
-      </c>
-      <c r="C630" t="inlineStr"/>
-      <c r="D630" t="inlineStr"/>
-      <c r="E630" t="inlineStr"/>
+      <c r="A630" t="n">
+        <v>34</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Mads Hermansen</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>34</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Gabriel dos Santos Magalhães</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -14088,12 +14116,12 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Mads Hermansen</t>
+          <t>Konstantinos Mavropanos</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -14103,7 +14131,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -14113,7 +14141,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Gabriel dos Santos Magalhães</t>
+          <t>Omar Alderete</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -14128,7 +14156,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -14138,12 +14166,12 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Konstantinos Mavropanos</t>
+          <t>Bruno Borges Fernandes</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -14153,32 +14181,32 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="635">
-      <c r="A635" t="n">
+      <c r="A635" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>Omar Alderete</t>
-        </is>
-      </c>
-      <c r="C635" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D635" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E635" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B635" s="3" t="inlineStr">
+        <is>
+          <t>Cody Gakpo</t>
+        </is>
+      </c>
+      <c r="C635" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D635" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E635" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -14188,7 +14216,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Dominik Szoboszlai</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -14203,57 +14231,57 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="637">
-      <c r="A637" s="3" t="n">
+      <c r="A637" t="n">
         <v>34</v>
       </c>
-      <c r="B637" s="3" t="inlineStr">
-        <is>
-          <t>Cody Gakpo</t>
-        </is>
-      </c>
-      <c r="C637" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D637" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E637" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Eberechi Eze</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="638">
-      <c r="A638" t="n">
+      <c r="A638" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>Dominik Szoboszlai</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D638" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E638" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="B638" s="4" t="inlineStr">
+        <is>
+          <t>Mohamed Salah</t>
+        </is>
+      </c>
+      <c r="C638" s="4" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D638" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E638" s="4" t="inlineStr">
+        <is>
+          <t>1 (2)</t>
         </is>
       </c>
     </row>
@@ -14263,12 +14291,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Eberechi Eze</t>
+          <t>Dominic Solanke-Mitchell</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -14278,32 +14306,32 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="640">
-      <c r="A640" s="4" t="n">
+      <c r="A640" t="n">
         <v>34</v>
       </c>
-      <c r="B640" s="4" t="inlineStr">
-        <is>
-          <t>Mohamed Salah</t>
-        </is>
-      </c>
-      <c r="C640" s="4" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D640" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E640" s="4" t="inlineStr">
-        <is>
-          <t>1 (2)</t>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Kai Havertz</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -14313,22 +14341,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Dominic Solanke-Mitchell</t>
+          <t>Matz Sels</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -14338,22 +14366,22 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Kai Havertz</t>
+          <t>El Hadji Malick Diouf</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -14363,12 +14391,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Matz Sels</t>
+          <t>Luke O'Nien</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -14378,7 +14406,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14416,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Luke Shaw</t>
+          <t>Brian Brobbey</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -14403,80 +14431,52 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="645">
-      <c r="A645" t="n">
-        <v>34</v>
-      </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>El Hadji Malick Diouf</t>
-        </is>
-      </c>
-      <c r="C645" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D645" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E645" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="A645" s="5" t="inlineStr">
+        <is>
+          <t>GW34 TOTAL</t>
+        </is>
+      </c>
+      <c r="B645" s="5" t="inlineStr"/>
+      <c r="C645" s="5" t="inlineStr"/>
+      <c r="D645" s="5" t="inlineStr"/>
+      <c r="E645" s="5" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="646">
-      <c r="A646" t="n">
-        <v>34</v>
-      </c>
+      <c r="A646" t="inlineStr"/>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Brian Brobbey</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D646" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E646" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Eberechi Eze in for Marcus Tavernier</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr"/>
+      <c r="D646" t="inlineStr"/>
+      <c r="E646" t="inlineStr"/>
     </row>
     <row r="647">
-      <c r="A647" s="5" t="inlineStr">
-        <is>
-          <t>GW34 TOTAL</t>
-        </is>
-      </c>
-      <c r="B647" s="5" t="inlineStr"/>
-      <c r="C647" s="5" t="inlineStr"/>
-      <c r="D647" s="5" t="inlineStr"/>
-      <c r="E647" s="5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="A647" t="inlineStr"/>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Matz Sels in for Bart Verbruggen</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr"/>
+      <c r="D647" t="inlineStr"/>
+      <c r="E647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr"/>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Eberechi Eze in for Marcus Tavernier</t>
+          <t>Gabriel dos Santos Magalhães in for Jan Paul van Hecke</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -14487,7 +14487,7 @@
       <c r="A649" t="inlineStr"/>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Matz Sels in for Bart Verbruggen</t>
+          <t>Mohamed Salah in for Diego Gómez Amarilla</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -14498,7 +14498,7 @@
       <c r="A650" t="inlineStr"/>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Gabriel dos Santos Magalhães in for Jan Paul van Hecke</t>
+          <t>Dominik Szoboszlai in for Enzo Fernández</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -14509,7 +14509,7 @@
       <c r="A651" t="inlineStr"/>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Mohamed Salah in for Diego Gómez Amarilla</t>
+          <t>Kai Havertz in for João Pedro Junqueira de Jesus</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
@@ -14520,7 +14520,7 @@
       <c r="A652" t="inlineStr"/>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Dominik Szoboszlai in for Enzo Fernández</t>
+          <t>Luke O'Nien in for Marc Guéhi</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -14531,7 +14531,7 @@
       <c r="A653" t="inlineStr"/>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Kai Havertz in for João Pedro Junqueira de Jesus</t>
+          <t>Mads Hermansen in for Karl Darlow</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -14542,7 +14542,7 @@
       <c r="A654" t="inlineStr"/>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Luke Shaw in for Marc Guéhi</t>
+          <t>El Hadji Malick Diouf in for Jaka Bijol</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -14553,7 +14553,7 @@
       <c r="A655" t="inlineStr"/>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Mads Hermansen in for Karl Darlow</t>
+          <t>Konstantinos Mavropanos in for Virgil van Dijk</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -14564,7 +14564,7 @@
       <c r="A656" t="inlineStr"/>
       <c r="B656" t="inlineStr">
         <is>
-          <t>El Hadji Malick Diouf in for Jaka Bijol</t>
+          <t>Omar Alderete in for Nico O'Reilly</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
@@ -14575,7 +14575,7 @@
       <c r="A657" t="inlineStr"/>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Konstantinos Mavropanos in for Virgil van Dijk</t>
+          <t>Dominic Solanke-Mitchell in for Erling Haaland</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -14586,7 +14586,7 @@
       <c r="A658" t="inlineStr"/>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Omar Alderete in for Nico O'Reilly</t>
+          <t>Brian Brobbey in for Dominic Calvert-Lewin</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -14595,36 +14595,64 @@
     </row>
     <row r="659">
       <c r="A659" t="inlineStr"/>
-      <c r="B659" t="inlineStr">
-        <is>
-          <t>Dominic Solanke-Mitchell in for Erling Haaland</t>
+      <c r="B659" s="1" t="inlineStr">
+        <is>
+          <t>CHIP: Free Hit</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr"/>
       <c r="E659" t="inlineStr"/>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr"/>
-      <c r="B660" t="inlineStr">
-        <is>
-          <t>Brian Brobbey in for Dominic Calvert-Lewin</t>
-        </is>
-      </c>
-      <c r="C660" t="inlineStr"/>
-      <c r="D660" t="inlineStr"/>
-      <c r="E660" t="inlineStr"/>
-    </row>
     <row r="661">
-      <c r="A661" t="inlineStr"/>
-      <c r="B661" s="1" t="inlineStr">
-        <is>
-          <t>CHIP: Free Hit</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr"/>
-      <c r="D661" t="inlineStr"/>
-      <c r="E661" t="inlineStr"/>
+      <c r="A661" t="n">
+        <v>35</v>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Karl Darlow</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B662" s="3" t="inlineStr">
+        <is>
+          <t>Gabriel dos Santos Magalhães</t>
+        </is>
+      </c>
+      <c r="C662" s="3" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D662" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E662" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
@@ -14632,12 +14660,12 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Karl Darlow</t>
+          <t>Marc Guéhi</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -14647,32 +14675,32 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="664">
-      <c r="A664" s="3" t="n">
+      <c r="A664" t="n">
         <v>35</v>
       </c>
-      <c r="B664" s="3" t="inlineStr">
-        <is>
-          <t>Gabriel dos Santos Magalhães</t>
-        </is>
-      </c>
-      <c r="C664" s="3" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D664" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E664" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Nico O'Reilly</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -14682,12 +14710,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Marc Guéhi</t>
+          <t>Bruno Borges Fernandes</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -14697,7 +14725,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -14707,12 +14735,12 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Nico O'Reilly</t>
+          <t>Cody Gakpo</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -14722,7 +14750,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -14732,7 +14760,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Dango Ouattara</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -14747,7 +14775,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -14757,7 +14785,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Cody Gakpo</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -14772,7 +14800,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14810,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Dango Ouattara</t>
+          <t>Marcus Tavernier</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -14797,7 +14825,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -14807,12 +14835,12 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Enzo Fernández</t>
+          <t>Dominic Calvert-Lewin</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -14822,32 +14850,32 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="671">
-      <c r="A671" t="n">
+      <c r="A671" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>Marcus Tavernier</t>
-        </is>
-      </c>
-      <c r="C671" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D671" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E671" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="B671" s="4" t="inlineStr">
+        <is>
+          <t>Erling Haaland</t>
+        </is>
+      </c>
+      <c r="C671" s="4" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D671" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E671" s="4" t="inlineStr">
+        <is>
+          <t>7 (14)</t>
         </is>
       </c>
     </row>
@@ -14857,47 +14885,47 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Dominic Calvert-Lewin</t>
+          <t>Bart Verbruggen</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="673">
-      <c r="A673" s="4" t="n">
+      <c r="A673" t="n">
         <v>35</v>
       </c>
-      <c r="B673" s="4" t="inlineStr">
-        <is>
-          <t>Erling Haaland</t>
-        </is>
-      </c>
-      <c r="C673" s="4" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D673" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E673" s="4" t="inlineStr">
-        <is>
-          <t>7 (14)</t>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Jan Paul van Hecke</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Bench</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -14907,12 +14935,12 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Bart Verbruggen</t>
+          <t>Jaka Bijol</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -14922,7 +14950,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -14932,12 +14960,12 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Jan Paul van Hecke</t>
+          <t>João Pedro Junqueira de Jesus</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -14947,96 +14975,96 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="676">
-      <c r="A676" t="n">
-        <v>35</v>
-      </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>Jaka Bijol</t>
-        </is>
-      </c>
-      <c r="C676" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D676" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E676" t="inlineStr">
-        <is>
-          <t>5</t>
+      <c r="A676" s="5" t="inlineStr">
+        <is>
+          <t>GW35 TOTAL</t>
+        </is>
+      </c>
+      <c r="B676" s="5" t="inlineStr"/>
+      <c r="C676" s="5" t="inlineStr"/>
+      <c r="D676" s="5" t="inlineStr"/>
+      <c r="E676" s="5" t="inlineStr">
+        <is>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="677">
-      <c r="A677" t="n">
-        <v>35</v>
-      </c>
+      <c r="A677" t="inlineStr"/>
       <c r="B677" t="inlineStr">
         <is>
-          <t>João Pedro Junqueira de Jesus</t>
-        </is>
-      </c>
-      <c r="C677" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D677" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E677" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Dango Ouattara in for Diego Gómez Amarilla</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr"/>
+      <c r="D677" t="inlineStr"/>
+      <c r="E677" t="inlineStr"/>
     </row>
     <row r="678">
-      <c r="A678" s="5" t="inlineStr">
-        <is>
-          <t>GW35 TOTAL</t>
-        </is>
-      </c>
-      <c r="B678" s="5" t="inlineStr"/>
-      <c r="C678" s="5" t="inlineStr"/>
-      <c r="D678" s="5" t="inlineStr"/>
-      <c r="E678" s="5" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="inlineStr"/>
-      <c r="B679" t="inlineStr">
-        <is>
-          <t>Dango Ouattara in for Diego Gómez Amarilla</t>
-        </is>
-      </c>
-      <c r="C679" t="inlineStr"/>
-      <c r="D679" t="inlineStr"/>
-      <c r="E679" t="inlineStr"/>
+      <c r="A678" t="inlineStr"/>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Gabriel dos Santos Magalhães in for Virgil van Dijk</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr"/>
+      <c r="D678" t="inlineStr"/>
+      <c r="E678" t="inlineStr"/>
     </row>
     <row r="680">
-      <c r="A680" t="inlineStr"/>
+      <c r="A680" t="n">
+        <v>36</v>
+      </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Gabriel dos Santos Magalhães in for Virgil van Dijk</t>
-        </is>
-      </c>
-      <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr"/>
-      <c r="E680" t="inlineStr"/>
+          <t>Bart Verbruggen</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>36</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Gabriel dos Santos Magalhães</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -15044,12 +15072,12 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Bart Verbruggen</t>
+          <t>Jan Paul van Hecke</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -15069,7 +15097,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Gabriel dos Santos Magalhães</t>
+          <t>Marc Guéhi</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -15084,7 +15112,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -15094,7 +15122,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Jan Paul van Hecke</t>
+          <t>Maxence Lacroix</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -15109,32 +15137,32 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="685">
-      <c r="A685" t="n">
+      <c r="A685" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B685" t="inlineStr">
-        <is>
-          <t>Marc Guéhi</t>
-        </is>
-      </c>
-      <c r="C685" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D685" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E685" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="B685" s="3" t="inlineStr">
+        <is>
+          <t>Nico O'Reilly</t>
+        </is>
+      </c>
+      <c r="C685" s="3" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D685" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E685" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -15144,12 +15172,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Maxence Lacroix</t>
+          <t>Bruno Borges Fernandes</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -15159,32 +15187,32 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="687">
-      <c r="A687" s="3" t="n">
+      <c r="A687" t="n">
         <v>36</v>
       </c>
-      <c r="B687" s="3" t="inlineStr">
-        <is>
-          <t>Nico O'Reilly</t>
-        </is>
-      </c>
-      <c r="C687" s="3" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D687" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E687" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Cody Gakpo</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -15194,7 +15222,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Dango Ouattara</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -15209,7 +15237,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15247,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Cody Gakpo</t>
+          <t>Marcus Tavernier</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -15239,27 +15267,27 @@
       </c>
     </row>
     <row r="690">
-      <c r="A690" t="n">
+      <c r="A690" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B690" t="inlineStr">
-        <is>
-          <t>Dango Ouattara</t>
-        </is>
-      </c>
-      <c r="C690" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D690" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E690" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="B690" s="4" t="inlineStr">
+        <is>
+          <t>Erling Haaland</t>
+        </is>
+      </c>
+      <c r="C690" s="4" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D690" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E690" s="4" t="inlineStr">
+        <is>
+          <t>11 (22)</t>
         </is>
       </c>
     </row>
@@ -15269,17 +15297,17 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Marcus Tavernier</t>
+          <t>Karl Darlow</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
@@ -15289,27 +15317,27 @@
       </c>
     </row>
     <row r="692">
-      <c r="A692" s="4" t="n">
+      <c r="A692" t="n">
         <v>36</v>
       </c>
-      <c r="B692" s="4" t="inlineStr">
-        <is>
-          <t>Erling Haaland</t>
-        </is>
-      </c>
-      <c r="C692" s="4" t="inlineStr">
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Dominic Calvert-Lewin</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
         <is>
           <t>FWD</t>
         </is>
       </c>
-      <c r="D692" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E692" s="4" t="inlineStr">
-        <is>
-          <t>11 (22)</t>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Bench</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -15319,12 +15347,12 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Karl Darlow</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -15334,7 +15362,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -15344,7 +15372,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Dominic Calvert-Lewin</t>
+          <t>João Pedro Junqueira de Jesus</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -15359,85 +15387,85 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="695">
-      <c r="A695" t="n">
-        <v>36</v>
-      </c>
-      <c r="B695" t="inlineStr">
-        <is>
-          <t>Enzo Fernández</t>
-        </is>
-      </c>
-      <c r="C695" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D695" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E695" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="A695" s="5" t="inlineStr">
+        <is>
+          <t>GW36 TOTAL</t>
+        </is>
+      </c>
+      <c r="B695" s="5" t="inlineStr"/>
+      <c r="C695" s="5" t="inlineStr"/>
+      <c r="D695" s="5" t="inlineStr"/>
+      <c r="E695" s="5" t="inlineStr">
+        <is>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="696">
-      <c r="A696" t="n">
-        <v>36</v>
-      </c>
+      <c r="A696" t="inlineStr"/>
       <c r="B696" t="inlineStr">
         <is>
-          <t>João Pedro Junqueira de Jesus</t>
-        </is>
-      </c>
-      <c r="C696" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D696" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E696" t="inlineStr">
+          <t>Maxence Lacroix in for Jaka Bijol</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr"/>
+      <c r="D696" t="inlineStr"/>
+      <c r="E696" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>37</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Bart Verbruggen</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" s="5" t="inlineStr">
-        <is>
-          <t>GW36 TOTAL</t>
-        </is>
-      </c>
-      <c r="B697" s="5" t="inlineStr"/>
-      <c r="C697" s="5" t="inlineStr"/>
-      <c r="D697" s="5" t="inlineStr"/>
-      <c r="E697" s="5" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="inlineStr"/>
-      <c r="B698" t="inlineStr">
-        <is>
-          <t>Maxence Lacroix in for Jaka Bijol</t>
-        </is>
-      </c>
-      <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr"/>
-      <c r="E698" t="inlineStr"/>
+    <row r="699">
+      <c r="A699" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B699" s="4" t="inlineStr">
+        <is>
+          <t>Gabriel dos Santos Magalhães</t>
+        </is>
+      </c>
+      <c r="C699" s="4" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D699" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E699" s="4" t="inlineStr">
+        <is>
+          <t>6 (12)</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
@@ -15445,12 +15473,12 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Bart Verbruggen</t>
+          <t>Jan Paul van Hecke</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -15465,27 +15493,27 @@
       </c>
     </row>
     <row r="701">
-      <c r="A701" s="4" t="n">
+      <c r="A701" t="n">
         <v>37</v>
       </c>
-      <c r="B701" s="4" t="inlineStr">
-        <is>
-          <t>Gabriel dos Santos Magalhães</t>
-        </is>
-      </c>
-      <c r="C701" s="4" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D701" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E701" s="4" t="inlineStr">
-        <is>
-          <t>6 (12)</t>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Marc Guéhi</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15523,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Jan Paul van Hecke</t>
+          <t>Nico O'Reilly</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -15520,12 +15548,12 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Marc Guéhi</t>
+          <t>Bruno Borges Fernandes</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -15535,7 +15563,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -15545,12 +15573,12 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Nico O'Reilly</t>
+          <t>Dango Ouattara</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -15560,7 +15588,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -15570,7 +15598,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -15585,7 +15613,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -15595,7 +15623,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Dango Ouattara</t>
+          <t>Leandro Trossard</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -15610,7 +15638,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -15620,12 +15648,12 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Enzo Fernández</t>
+          <t>Dominic Calvert-Lewin</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -15635,32 +15663,32 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="708">
-      <c r="A708" t="n">
+      <c r="A708" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B708" t="inlineStr">
-        <is>
-          <t>Leandro Trossard</t>
-        </is>
-      </c>
-      <c r="C708" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D708" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E708" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="B708" s="3" t="inlineStr">
+        <is>
+          <t>Erling Haaland</t>
+        </is>
+      </c>
+      <c r="C708" s="3" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D708" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E708" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -15670,47 +15698,47 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Dominic Calvert-Lewin</t>
+          <t>Karl Darlow</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="710">
-      <c r="A710" s="3" t="n">
+      <c r="A710" t="n">
         <v>37</v>
       </c>
-      <c r="B710" s="3" t="inlineStr">
-        <is>
-          <t>Erling Haaland</t>
-        </is>
-      </c>
-      <c r="C710" s="3" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D710" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E710" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Marcus Tavernier</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Bench</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -15720,12 +15748,12 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Karl Darlow</t>
+          <t>Maxence Lacroix</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -15735,7 +15763,7 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -15745,12 +15773,12 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Marcus Tavernier</t>
+          <t>João Pedro Junqueira de Jesus</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -15760,85 +15788,85 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="5" t="inlineStr">
+        <is>
+          <t>GW37 TOTAL</t>
+        </is>
+      </c>
+      <c r="B713" s="5" t="inlineStr"/>
+      <c r="C713" s="5" t="inlineStr"/>
+      <c r="D713" s="5" t="inlineStr"/>
+      <c r="E713" s="5" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr"/>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Leandro Trossard in for Cody Gakpo</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr"/>
+      <c r="D714" t="inlineStr"/>
+      <c r="E714" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>38</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Bart Verbruggen</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="n">
-        <v>37</v>
-      </c>
-      <c r="B713" t="inlineStr">
-        <is>
-          <t>Maxence Lacroix</t>
-        </is>
-      </c>
-      <c r="C713" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D713" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E713" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="n">
-        <v>37</v>
-      </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>João Pedro Junqueira de Jesus</t>
-        </is>
-      </c>
-      <c r="C714" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D714" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E714" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" s="5" t="inlineStr">
-        <is>
-          <t>GW37 TOTAL</t>
-        </is>
-      </c>
-      <c r="B715" s="5" t="inlineStr"/>
-      <c r="C715" s="5" t="inlineStr"/>
-      <c r="D715" s="5" t="inlineStr"/>
-      <c r="E715" s="5" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr"/>
-      <c r="B716" t="inlineStr">
-        <is>
-          <t>Leandro Trossard in for Cody Gakpo</t>
-        </is>
-      </c>
-      <c r="C716" t="inlineStr"/>
-      <c r="D716" t="inlineStr"/>
-      <c r="E716" t="inlineStr"/>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>38</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Gabriel dos Santos Magalhães</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
@@ -15846,12 +15874,12 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Bart Verbruggen</t>
+          <t>Jan Paul van Hecke</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -15861,32 +15889,32 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="719">
-      <c r="A719" t="n">
+      <c r="A719" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B719" t="inlineStr">
-        <is>
-          <t>Gabriel dos Santos Magalhães</t>
-        </is>
-      </c>
-      <c r="C719" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D719" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E719" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="B719" s="3" t="inlineStr">
+        <is>
+          <t>Nico O'Reilly</t>
+        </is>
+      </c>
+      <c r="C719" s="3" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D719" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E719" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -15896,12 +15924,12 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Jan Paul van Hecke</t>
+          <t>Bruno Borges Fernandes</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -15911,32 +15939,32 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="721">
-      <c r="A721" s="3" t="n">
+      <c r="A721" t="n">
         <v>38</v>
       </c>
-      <c r="B721" s="3" t="inlineStr">
-        <is>
-          <t>Nico O'Reilly</t>
-        </is>
-      </c>
-      <c r="C721" s="3" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D721" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E721" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Dango Ouattara</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -15946,7 +15974,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -15961,7 +15989,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -15971,7 +15999,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Dango Ouattara</t>
+          <t>Leandro Trossard</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -15986,7 +16014,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -15996,7 +16024,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Enzo Fernández</t>
+          <t>Marcus Tavernier</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -16011,7 +16039,7 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -16021,12 +16049,12 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Leandro Trossard</t>
+          <t>Dominic Calvert-Lewin</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -16036,7 +16064,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -16046,12 +16074,12 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Marcus Tavernier</t>
+          <t>Richarlison de Andrade</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -16061,7 +16089,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -16071,17 +16099,17 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Dominic Calvert-Lewin</t>
+          <t>Karl Darlow</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Starting 11</t>
+          <t>Bench</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
@@ -16096,47 +16124,47 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Richarlison de Andrade</t>
+          <t>Maxence Lacroix</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Bench</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B729" s="4" t="inlineStr">
+        <is>
+          <t>Erling Haaland</t>
+        </is>
+      </c>
+      <c r="C729" s="4" t="inlineStr">
+        <is>
           <t>FWD</t>
         </is>
       </c>
-      <c r="D728" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E728" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="n">
-        <v>38</v>
-      </c>
-      <c r="B729" t="inlineStr">
-        <is>
-          <t>Karl Darlow</t>
-        </is>
-      </c>
-      <c r="C729" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
-      <c r="D729" t="inlineStr">
+      <c r="D729" s="4" t="inlineStr">
         <is>
           <t>Bench</t>
         </is>
       </c>
-      <c r="E729" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="E729" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -16146,7 +16174,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Maxence Lacroix</t>
+          <t>Marc Guéhi</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -16166,192 +16194,142 @@
       </c>
     </row>
     <row r="731">
-      <c r="A731" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="B731" s="4" t="inlineStr">
-        <is>
-          <t>Erling Haaland</t>
-        </is>
-      </c>
-      <c r="C731" s="4" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D731" s="4" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E731" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="A731" s="5" t="inlineStr">
+        <is>
+          <t>GW38 TOTAL</t>
+        </is>
+      </c>
+      <c r="B731" s="5" t="inlineStr"/>
+      <c r="C731" s="5" t="inlineStr"/>
+      <c r="D731" s="5" t="inlineStr"/>
+      <c r="E731" s="5" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="732">
-      <c r="A732" t="n">
-        <v>38</v>
-      </c>
+      <c r="A732" t="inlineStr"/>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Marc Guéhi</t>
-        </is>
-      </c>
-      <c r="C732" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D732" t="inlineStr">
-        <is>
-          <t>Bench</t>
-        </is>
-      </c>
-      <c r="E732" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" s="5" t="inlineStr">
-        <is>
-          <t>GW38 TOTAL</t>
-        </is>
-      </c>
-      <c r="B733" s="5" t="inlineStr"/>
-      <c r="C733" s="5" t="inlineStr"/>
-      <c r="D733" s="5" t="inlineStr"/>
-      <c r="E733" s="5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>Richarlison de Andrade in for João Pedro Junqueira de Jesus</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr"/>
+      <c r="D732" t="inlineStr"/>
+      <c r="E732" t="inlineStr"/>
     </row>
     <row r="734">
-      <c r="A734" t="inlineStr"/>
-      <c r="B734" t="inlineStr">
-        <is>
-          <t>Richarlison de Andrade in for João Pedro Junqueira de Jesus</t>
-        </is>
-      </c>
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>RECONCILIATION</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr"/>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr"/>
       <c r="E734" t="inlineStr"/>
     </row>
+    <row r="735">
+      <c r="A735" t="inlineStr"/>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Sum of gameweek totals after hits (path)</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr"/>
+      <c r="D735" t="inlineStr"/>
+      <c r="E735" t="n">
+        <v>2160</v>
+      </c>
+    </row>
     <row r="736">
-      <c r="A736" s="1" t="inlineStr">
-        <is>
-          <t>RECONCILIATION</t>
-        </is>
-      </c>
-      <c r="B736" t="inlineStr"/>
+      <c r="A736" t="inlineStr"/>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>+ Bench Boost 1 bench points (GW10, chip read)</t>
+        </is>
+      </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr"/>
-      <c r="E736" t="inlineStr"/>
+      <c r="E736" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr"/>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Sum of gameweek totals after hits (path)</t>
+          <t>+ Bench Boost 2 bench points (GW33, chip read)</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr"/>
       <c r="E737" t="n">
-        <v>2131</v>
+        <v>28</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr"/>
       <c r="B738" t="inlineStr">
         <is>
-          <t>+ Bench Boost 1 bench points (GW10, chip read)</t>
+          <t>+ Triple Captain 1 read (GW17, post-hoc)</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr"/>
       <c r="E738" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr"/>
       <c r="B739" t="inlineStr">
         <is>
-          <t>+ Bench Boost 2 bench points (GW33, chip read)</t>
+          <t>Triple Captain 2 is IN the path (in-sim, GW26)</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
       <c r="D739" t="inlineStr"/>
       <c r="E739" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr"/>
-      <c r="B740" t="inlineStr">
-        <is>
-          <t>+ Triple Captain 1 read (GW17, post-hoc)</t>
-        </is>
+      <c r="B740">
+        <f> chip-inclusive total</f>
+        <v/>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr"/>
       <c r="E740" t="n">
-        <v>16</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr"/>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Triple Captain 2 is IN the path (in-sim, GW26)</t>
+          <t>Season figure on record</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr"/>
       <c r="E741" t="n">
-        <v>0</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr"/>
-      <c r="B742">
-        <f> chip-inclusive total</f>
-        <v/>
+      <c r="B742" s="1" t="inlineStr">
+        <is>
+          <t>RECONCILES</t>
+        </is>
       </c>
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr"/>
-      <c r="E742" t="n">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="inlineStr"/>
-      <c r="B743" t="inlineStr">
-        <is>
-          <t>Season figure on record</t>
-        </is>
-      </c>
-      <c r="C743" t="inlineStr"/>
-      <c r="D743" t="inlineStr"/>
-      <c r="E743" t="n">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="inlineStr"/>
-      <c r="B744" s="1" t="inlineStr">
-        <is>
-          <t>RECONCILES</t>
-        </is>
-      </c>
-      <c r="C744" t="inlineStr"/>
-      <c r="D744" t="inlineStr"/>
-      <c r="E744" t="inlineStr"/>
+      <c r="E742" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
